--- a/www/flightdata/xlsx/eoss-325.xlsx
+++ b/www/flightdata/xlsx/eoss-325.xlsx
@@ -3777,7 +3777,7 @@
         <v>28398.22</v>
       </c>
       <c r="I2">
-        <v>662</v>
+        <v>493</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
